--- a/Commons/InventoryWebApp/src/main/webapp/WEB-INF/Templates/批量预出库导入模版.xlsx
+++ b/Commons/InventoryWebApp/src/main/webapp/WEB-INF/Templates/批量预出库导入模版.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>区域</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>领料人</t>
+  </si>
+  <si>
+    <t>项目经理</t>
   </si>
   <si>
     <t>请选择出库设备区域</t>
@@ -1088,7 +1091,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="19.375" customWidth="1"/>
@@ -1096,11 +1099,11 @@
     <col min="3" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="14.875" customWidth="1"/>
     <col min="7" max="7" width="15.75" customWidth="1"/>
-    <col min="8" max="9" width="17.875" customWidth="1"/>
-    <col min="10" max="10" width="60.875" customWidth="1"/>
+    <col min="8" max="10" width="17.875" customWidth="1"/>
+    <col min="11" max="11" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1128,19 +1131,22 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="4" t="s">
         <v>12</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Commons/InventoryWebApp/src/main/webapp/WEB-INF/Templates/批量预出库导入模版.xlsx
+++ b/Commons/InventoryWebApp/src/main/webapp/WEB-INF/Templates/批量预出库导入模版.xlsx
@@ -77,11 +77,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -727,11 +728,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -1097,41 +1104,41 @@
     <col min="1" max="1" width="19.375" customWidth="1"/>
     <col min="2" max="2" width="16.125" customWidth="1"/>
     <col min="3" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="14.875" customWidth="1"/>
+    <col min="6" max="6" width="14.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.75" customWidth="1"/>
     <col min="8" max="10" width="17.875" customWidth="1"/>
     <col min="11" max="11" width="60.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1139,20 +1146,23 @@
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
-      <formula1>1</formula1>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
+      <formula1>0</formula1>
       <formula2>99999</formula2>
     </dataValidation>
   </dataValidations>
